--- a/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
+++ b/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Lab-MolSSI_Revisions\Rotation 2\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/Documents/GitHub/CHE-3131/Rotation-2-Calorimetry/Sample-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD6FEEF-28A5-4552-8A3B-7BA88C4ACDF6}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2085" windowWidth="30900" windowHeight="8370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="8" r:id="rId1"/>
@@ -40,15 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>Time</t>
   </si>
   <si>
     <t>Temperature</t>
-  </si>
-  <si>
-    <t>Time (sec)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -98,8 +95,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.000000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -144,9 +141,9 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -432,16 +429,16 @@
   <dimension ref="A1:B902"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,6 +7659,7 @@
   <dimension ref="A1:B902"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14891,7 +14889,7 @@
   <dimension ref="A1:B902"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22130,22 +22128,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>114.97799999999999</v>
@@ -22162,7 +22160,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>5.0869999999999997</v>
@@ -22179,7 +22177,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <f>B2+B3</f>
@@ -22199,7 +22197,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1.0649999999999999</v>
@@ -22216,7 +22214,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
         <f>(B3/1.04)*B5/1000</f>
@@ -22275,21 +22273,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>114.97799999999999</v>
@@ -22306,7 +22304,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>5.0869999999999997</v>
@@ -22323,7 +22321,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <f>B2+B3</f>
@@ -22343,7 +22341,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1.0649999999999999</v>
@@ -22360,7 +22358,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
         <f>(B3/1.04)*B5/1000</f>
@@ -22381,7 +22379,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2">
         <f>89.44+4.184*B4</f>
@@ -22402,7 +22400,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>0.52170000000000005</v>
@@ -22419,7 +22417,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
         <f>B7*B8</f>
@@ -22440,7 +22438,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
         <f>-B9/(1000*B6)</f>

--- a/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
+++ b/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/Documents/GitHub/CHE-3131/Rotation-2-Calorimetry/Sample-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/Documents/GitHub/CHE-3131-Instructor/Rotation-2-Calorimetry/Sample-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD6FEEF-28A5-4552-8A3B-7BA88C4ACDF6}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18734FB0-B0CC-4D4B-AD89-753134DC2DAE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2085" windowWidth="30900" windowHeight="8370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial 1" sheetId="8" r:id="rId1"/>
@@ -40,15 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>Time</t>
   </si>
   <si>
     <t>Temperature</t>
-  </si>
-  <si>
-    <t>temperature</t>
   </si>
   <si>
     <t>Mass HCl (g)</t>
@@ -98,7 +95,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +114,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -139,13 +142,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -161,6 +165,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -438,7 +446,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -22128,22 +22136,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>114.97799999999999</v>
@@ -22160,7 +22168,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>5.0869999999999997</v>
@@ -22177,7 +22185,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <f>B2+B3</f>
@@ -22197,7 +22205,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>1.0649999999999999</v>
@@ -22214,7 +22222,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <f>(B3/1.04)*B5/1000</f>
@@ -22263,7 +22271,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5069A9-9134-4256-84DE-21F513523AB1}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -22271,23 +22279,23 @@
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
       <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>114.97799999999999</v>
@@ -22302,9 +22310,9 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>5.0869999999999997</v>
@@ -22319,9 +22327,9 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <f>B2+B3</f>
@@ -22339,9 +22347,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>1.0649999999999999</v>
@@ -22356,9 +22364,9 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <f>(B3/1.04)*B5/1000</f>
@@ -22377,9 +22385,9 @@
         <v>5.1201923076923078E-6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2">
         <f>89.44+4.184*B4</f>
@@ -22398,9 +22406,9 @@
         <v>4.9320950508962264E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0.52170000000000005</v>
@@ -22414,10 +22422,11 @@
       <c r="E8">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4">
         <f>B7*B8</f>
@@ -22436,9 +22445,9 @@
         <v>20.638475880577793</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3">
         <f>-B9/(1000*B6)</f>

--- a/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
+++ b/Rotation-2-Calorimetry/Sample-Data/Calorimetry_SampleData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/Documents/GitHub/CHE-3131-Instructor/Rotation-2-Calorimetry/Sample-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofdallas-my.sharepoint.com/personal/pmpatel_udallas_edu/Documents/Documents/GitHub/CHE-3131/Rotation-2-Calorimetry/Sample-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18734FB0-B0CC-4D4B-AD89-753134DC2DAE}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{601AE5CF-85FB-41AB-858C-FE3A9BF747F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C107C43-C8DC-40C3-AECC-30E3A0B579E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t>Time</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>[NaOH] (M)</t>
-  </si>
-  <si>
-    <t>uncertainty</t>
   </si>
   <si>
     <t>Total Mass (g)</t>
@@ -142,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -150,6 +147,24 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -165,10 +180,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22135,111 +22146,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
+        <v>114.97799999999999</v>
+      </c>
+      <c r="C2" s="7">
+        <v>109.955</v>
+      </c>
+      <c r="D2" s="7">
+        <v>105.098</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>5.0869999999999997</v>
+      </c>
+      <c r="C3" s="7">
+        <v>10.098000000000001</v>
+      </c>
+      <c r="D3" s="7">
+        <v>14.459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>114.97799999999999</v>
-      </c>
-      <c r="C2">
-        <v>109.955</v>
-      </c>
-      <c r="D2">
-        <v>105.098</v>
-      </c>
-      <c r="E2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>5.0869999999999997</v>
-      </c>
-      <c r="C3">
-        <v>10.098000000000001</v>
-      </c>
-      <c r="D3">
-        <v>14.459</v>
-      </c>
-      <c r="E3">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <f>B2+B3</f>
         <v>120.065</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <f t="shared" ref="C4:D4" si="0">C3+C2</f>
         <v>120.053</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <f t="shared" si="0"/>
         <v>119.557</v>
       </c>
-      <c r="E4">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="E5">
-        <v>6.5000000000000002E-2</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>(B3/1.04)*B5/1000</f>
         <v>5.209283653846152E-3</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="8">
         <f t="shared" ref="C6:D6" si="1">(C3/1.04)*C5/1000</f>
         <v>1.0340740384615384E-2</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="8">
         <f t="shared" si="1"/>
         <v>1.4806572115384614E-2</v>
       </c>
-      <c r="E6" s="1">
-        <f>B6*$E$3/B3</f>
-        <v>5.1201923076923061E-6</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
@@ -22280,191 +22274,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
+        <v>114.97799999999999</v>
+      </c>
+      <c r="C2" s="7">
+        <v>109.955</v>
+      </c>
+      <c r="D2" s="7">
+        <v>105.098</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>5.0869999999999997</v>
+      </c>
+      <c r="C3" s="7">
+        <v>10.098000000000001</v>
+      </c>
+      <c r="D3" s="7">
+        <v>14.459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>114.97799999999999</v>
-      </c>
-      <c r="C2">
-        <v>109.955</v>
-      </c>
-      <c r="D2">
-        <v>105.098</v>
-      </c>
-      <c r="E2">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>5.0869999999999997</v>
-      </c>
-      <c r="C3">
-        <v>10.098000000000001</v>
-      </c>
-      <c r="D3">
-        <v>14.459</v>
-      </c>
-      <c r="E3">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <f>B2+B3</f>
         <v>120.065</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <f t="shared" ref="C4:D4" si="0">C3+C2</f>
         <v>120.053</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <f t="shared" si="0"/>
         <v>119.557</v>
       </c>
-      <c r="E4">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>1.0649999999999999</v>
       </c>
-      <c r="E5">
-        <v>6.5000000000000002E-2</v>
-      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>(B3/1.04)*B5/1000</f>
         <v>5.209283653846152E-3</v>
       </c>
-      <c r="C6" s="1">
-        <f t="shared" ref="C6:D6" si="1">(C3/1.04)*C5/1000</f>
+      <c r="C6" s="8">
+        <f>(C3/1.04)*C5/1000</f>
         <v>1.0340740384615384E-2</v>
       </c>
-      <c r="D6" s="1">
-        <f t="shared" si="1"/>
+      <c r="D6" s="8">
+        <f t="shared" ref="C6:D6" si="1">(D3/1.04)*D5/1000</f>
         <v>1.4806572115384614E-2</v>
       </c>
-      <c r="E6" s="1">
-        <f>D6*E3/D3</f>
-        <v>5.1201923076923078E-6</v>
-      </c>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9">
         <f>89.44+4.184*B4</f>
         <v>591.79196000000002</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f t="shared" ref="C7:D7" si="2">89.44+4.184*C4</f>
         <v>591.74175200000002</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f t="shared" si="2"/>
         <v>589.66648800000007</v>
       </c>
-      <c r="E7" s="2">
-        <f>D7*E4/D4</f>
-        <v>4.9320950508962264E-2</v>
-      </c>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>0.52170000000000005</v>
-      </c>
-      <c r="C8">
-        <v>1.08</v>
-      </c>
-      <c r="D8">
-        <v>1.589</v>
-      </c>
-      <c r="E8">
-        <v>3.5000000000000003E-2</v>
+      <c r="A8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.52017999999999998</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1.0834699999999999</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.60514</v>
       </c>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="A9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11">
         <f>B7*B8</f>
-        <v>308.73786553200006</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" ref="C9:D9" si="3">C7*C8</f>
-        <v>639.08109216000003</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" si="3"/>
-        <v>936.9800494320001</v>
-      </c>
-      <c r="E9" s="4">
-        <f>D9*SQRT((E8/D8)^2+(E7/D7)^2)</f>
-        <v>20.638475880577793</v>
-      </c>
+        <v>307.83834175279998</v>
+      </c>
+      <c r="C9" s="11">
+        <f>C7*C8</f>
+        <v>641.13443603943995</v>
+      </c>
+      <c r="D9" s="11">
+        <f t="shared" ref="C9:D9" si="3">D7*D8</f>
+        <v>946.49726654832011</v>
+      </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="12">
         <f>-B9/(1000*B6)</f>
-        <v>-59.266856260370979</v>
-      </c>
-      <c r="C10" s="3">
+        <v>-59.094179201686352</v>
+      </c>
+      <c r="C10" s="12">
         <f>-C9/(1000*C6)</f>
-        <v>-61.802256742738081</v>
-      </c>
-      <c r="D10" s="3">
+        <v>-62.000825104680018</v>
+      </c>
+      <c r="D10" s="12">
         <f t="shared" ref="D10" si="4">-D9/(1000*D6)</f>
-        <v>-63.28136196077692</v>
-      </c>
-      <c r="E10" s="3">
-        <f>-1*C10*SQRT((E9/C9)^2+(E2/C2)^2)</f>
-        <v>1.9958431962651693</v>
-      </c>
+        <v>-63.924131741800799</v>
+      </c>
+      <c r="E10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
